--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0009_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0009_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1288,7 +1289,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.024613566998129346</v>
+        <v>0.024613566998129347</v>
       </c>
       <c r="B33" s="0">
         <v>0.70175438596491169</v>
@@ -1344,7 +1345,7 @@
         <v>0.072772259214787263</v>
       </c>
       <c r="G34" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H34" s="0">
         <v>0.48855308754189586</v>
@@ -1417,13 +1418,13 @@
         <v>1.2142367015722415</v>
       </c>
       <c r="F36" s="0">
-        <v>0.4675617654550081</v>
+        <v>0.46756176545500811</v>
       </c>
       <c r="G36" s="0">
         <v>0.56326694830014024</v>
       </c>
       <c r="H36" s="0">
-        <v>1.3974890643640276</v>
+        <v>1.3974890643640277</v>
       </c>
       <c r="I36" s="0">
         <v>1.2591606919425622</v>
@@ -1440,7 +1441,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.76794329034163566</v>
+        <v>0.76794329034163567</v>
       </c>
       <c r="B37" s="0">
         <v>5.8771929824561351</v>
@@ -1481,7 +1482,7 @@
         <v>1.1937579994092733</v>
       </c>
       <c r="B38" s="0">
-        <v>6.6666666666666607</v>
+        <v>6.6666666666666608</v>
       </c>
       <c r="C38" s="0">
         <v>2.6414232998135891</v>
@@ -1534,7 +1535,7 @@
         <v>2.044900483935522</v>
       </c>
       <c r="G39" s="0">
-        <v>3.1985515992757962</v>
+        <v>3.1985515992757963</v>
       </c>
       <c r="H39" s="0">
         <v>3.8913821507697519</v>
@@ -1546,7 +1547,7 @@
         <v>2.8708133971291843</v>
       </c>
       <c r="K39" s="0">
-        <v>8.2474226804123631</v>
+        <v>8.2474226804123632</v>
       </c>
       <c r="L39" s="0">
         <v>2.4321214194631895</v>
@@ -1739,7 +1740,7 @@
         <v>7.7319587628865918</v>
       </c>
       <c r="L44" s="0">
-        <v>4.2266662519827038</v>
+        <v>4.2266662519827039</v>
       </c>
     </row>
     <row r="45">
@@ -1777,7 +1778,7 @@
         <v>7.7319587628865918</v>
       </c>
       <c r="L45" s="0">
-        <v>4.0727148322084989</v>
+        <v>4.072714832208499</v>
       </c>
     </row>
     <row r="46">
@@ -1803,7 +1804,7 @@
         <v>2.7761013880506913</v>
       </c>
       <c r="H46" s="0">
-        <v>2.5336590353916923</v>
+        <v>2.5336590353916924</v>
       </c>
       <c r="I46" s="0">
         <v>4.0972373934976432</v>
@@ -1896,7 +1897,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>3.2243772767549443</v>
+        <v>3.2243772767549444</v>
       </c>
       <c r="B49" s="0">
         <v>0.61403508771929771</v>
@@ -1972,7 +1973,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>2.9610121098749604</v>
+        <v>2.9610121098749605</v>
       </c>
       <c r="B51" s="0">
         <v>0.61403508771929771</v>
@@ -1984,7 +1985,7 @@
         <v>3.3803765056620074</v>
       </c>
       <c r="E51" s="0">
-        <v>2.808556341179627</v>
+        <v>2.8085563411796271</v>
       </c>
       <c r="F51" s="0">
         <v>2.8854200778663146</v>
@@ -2238,13 +2239,13 @@
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>2.3481342916215397</v>
+        <v>2.3481342916215398</v>
       </c>
       <c r="B58" s="0">
         <v>2.8947368421052606</v>
       </c>
       <c r="C58" s="0">
-        <v>2.0061121748944299</v>
+        <v>2.00611217489443</v>
       </c>
       <c r="D58" s="0">
         <v>1.8224220421705559</v>
@@ -2352,7 +2353,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>2.2127596731318286</v>
+        <v>2.2127596731318287</v>
       </c>
       <c r="B61" s="0">
         <v>1.3157894736842093</v>
@@ -2478,10 +2479,10 @@
         <v>1.30550813838867</v>
       </c>
       <c r="E64" s="0">
-        <v>1.7232017661624734</v>
+        <v>1.7232017661624735</v>
       </c>
       <c r="F64" s="0">
-        <v>1.6864971073026946</v>
+        <v>1.6864971073026947</v>
       </c>
       <c r="G64" s="0">
         <v>1.3277006638503308</v>
@@ -2525,7 +2526,7 @@
         <v>1.4484007242003607</v>
       </c>
       <c r="H65" s="0">
-        <v>1.3577231153780593</v>
+        <v>1.3577231153780594</v>
       </c>
       <c r="I65" s="0">
         <v>1.1459553931401552</v>
@@ -2624,7 +2625,7 @@
         <v>0.087719298245613961</v>
       </c>
       <c r="C68" s="0">
-        <v>1.1729796218567305</v>
+        <v>1.1729796218567306</v>
       </c>
       <c r="D68" s="0">
         <v>0.72848796672516947</v>
@@ -2908,7 +2909,7 @@
         <v>0.8634891779810252</v>
       </c>
       <c r="I75" s="0">
-        <v>0.61965005660264882</v>
+        <v>0.61965005660264883</v>
       </c>
       <c r="J75" s="0">
         <v>1.0121457489878534</v>
@@ -2972,7 +2973,7 @@
         <v>0.28129733368595655</v>
       </c>
       <c r="E77" s="0">
-        <v>0.60980339508935177</v>
+        <v>0.60980339508935178</v>
       </c>
       <c r="F77" s="0">
         <v>0.82414583560746568</v>
@@ -3057,7 +3058,7 @@
         <v>0.48280024140012029</v>
       </c>
       <c r="H79" s="0">
-        <v>0.70442538203715221</v>
+        <v>0.70442538203715222</v>
       </c>
       <c r="I79" s="0">
         <v>0.38728128537665557</v>
@@ -3183,7 +3184,7 @@
         <v>0.12886597938144462</v>
       </c>
       <c r="L82" s="0">
-        <v>0.51939165863217029</v>
+        <v>0.5193916586321703</v>
       </c>
     </row>
     <row r="83">
@@ -3212,7 +3213,7 @@
         <v>0.53968073623814072</v>
       </c>
       <c r="I83" s="0">
-        <v>0.26414569720561631</v>
+        <v>0.26414569720561632</v>
       </c>
       <c r="J83" s="0">
         <v>0.36805299963194671</v>
@@ -3270,7 +3271,7 @@
         <v>0.17543859649122792</v>
       </c>
       <c r="C85" s="0">
-        <v>0.20162568635158939</v>
+        <v>0.2016256863515894</v>
       </c>
       <c r="D85" s="0">
         <v>0.16589329935325642</v>
@@ -3434,7 +3435,7 @@
         <v>0.28381181093767033</v>
       </c>
       <c r="G89" s="0">
-        <v>0.32186682760008017</v>
+        <v>0.32186682760008018</v>
       </c>
       <c r="H89" s="0">
         <v>0.23859569391580959</v>
